--- a/Excel/StoneConfig.xlsx
+++ b/Excel/StoneConfig.xlsx
@@ -1197,7 +1197,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
       <c r="H7" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1251,7 +1251,7 @@
         <v>15</v>
       </c>
       <c r="H8" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
@@ -1307,7 +1307,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
@@ -1335,7 +1335,7 @@
         <v>21</v>
       </c>
       <c r="H11" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
@@ -1363,7 +1363,7 @@
         <v>23</v>
       </c>
       <c r="H12" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -1391,7 +1391,7 @@
         <v>25</v>
       </c>
       <c r="H13" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>27</v>
       </c>
       <c r="H14" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
@@ -1447,7 +1447,7 @@
         <v>29</v>
       </c>
       <c r="H15" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>

--- a/Excel/StoneConfig.xlsx
+++ b/Excel/StoneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1197,7 +1197,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
       <c r="H7" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1251,7 +1251,7 @@
         <v>15</v>
       </c>
       <c r="H8" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
@@ -1335,7 +1335,7 @@
         <v>21</v>
       </c>
       <c r="H11" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
@@ -1363,7 +1363,7 @@
         <v>23</v>
       </c>
       <c r="H12" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -1391,7 +1391,7 @@
         <v>25</v>
       </c>
       <c r="H13" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>27</v>
       </c>
       <c r="H14" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
@@ -1447,7 +1447,7 @@
         <v>29</v>
       </c>
       <c r="H15" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>

--- a/Excel/StoneConfig.xlsx
+++ b/Excel/StoneConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -117,6 +120,57 @@
   </si>
   <si>
     <t>2012</t>
+  </si>
+  <si>
+    <t>极·攻击宝石</t>
+  </si>
+  <si>
+    <t>极·韧性宝石</t>
+  </si>
+  <si>
+    <t>极·生命宝石</t>
+  </si>
+  <si>
+    <t>极·命中宝石</t>
+  </si>
+  <si>
+    <t>极·闪避宝石</t>
+  </si>
+  <si>
+    <t>极·物攻宝石</t>
+  </si>
+  <si>
+    <t>极·魔攻宝石</t>
+  </si>
+  <si>
+    <t>极·道攻宝石</t>
+  </si>
+  <si>
+    <t>极·增伤宝石</t>
+  </si>
+  <si>
+    <t>极·破韧宝石</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>极·物伤宝石</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>极·魔伤宝石</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>极·道伤宝石</t>
+  </si>
+  <si>
+    <t>2009</t>
   </si>
 </sst>
 </file>
@@ -1090,19 +1144,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M55"/>
+  <dimension ref="A3:N56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="1" customWidth="1"/>
-    <col min="9" max="10" width="13.25" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="9.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.875" style="1" customWidth="1"/>
+    <col min="10" max="11" width="13.25" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1127,8 +1181,11 @@
       <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1153,517 +1210,879 @@
       <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
+        <v>9</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
         <v>60000001</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="2">
         <v>10</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="2">
-        <v>5</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1</v>
-      </c>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4">
-        <v>60000002</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="2">
-        <v>10</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
       <c r="J7" s="2">
         <v>1</v>
       </c>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
         <v>60000003</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2">
         <v>15</v>
       </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
       <c r="J8" s="2">
         <v>1</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
         <v>3</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>60000004</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="2">
-        <v>1</v>
+      <c r="H9" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
       </c>
       <c r="J9" s="2">
-        <v>2</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
         <v>3</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <v>60000005</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="2">
-        <v>2</v>
+      <c r="H10" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="I10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>2</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
         <v>60000006</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="2">
         <v>8</v>
       </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
       <c r="J11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:13">
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:14">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
         <v>60000007</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="2">
         <v>8</v>
       </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
       <c r="J12" s="2">
         <v>1</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" customHeight="1" spans="3:13">
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="4"/>
+    </row>
+    <row r="13" customHeight="1" spans="3:14">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
         <v>60000008</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="2">
         <v>8</v>
       </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
       <c r="J13" s="2">
         <v>1</v>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="4"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:14">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
         <v>60000009</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
       <c r="J14" s="2">
         <v>1</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" customHeight="1" spans="3:13">
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="4"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:14">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
         <v>60000010</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2">
         <v>5</v>
       </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
       <c r="J15" s="2">
         <v>1</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="4"/>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:13">
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2"/>
+      <c r="N15" s="4"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="4"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="5:13">
-      <c r="E17" s="4"/>
-      <c r="F17" s="1"/>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:13">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="4"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="5:13">
-      <c r="E19" s="4"/>
-      <c r="F19" s="1"/>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="5:13">
-      <c r="E20" s="4"/>
-      <c r="F20" s="1"/>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="4"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:13">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="4"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C17" s="1">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>11</v>
+      </c>
+      <c r="F17" s="4">
+        <v>60000011</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="2">
+        <v>10</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="M17" s="2"/>
+      <c r="N17" s="4"/>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>12</v>
+      </c>
+      <c r="F18" s="4">
+        <v>60000012</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="N18" s="4"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:14">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="1">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>12</v>
+      </c>
+      <c r="F19" s="4">
+        <v>60000013</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="2">
+        <v>30</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="4"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C20" s="1">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>13</v>
+      </c>
+      <c r="F20" s="4">
+        <v>60000014</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2</v>
+      </c>
+      <c r="N20" s="4"/>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>13</v>
+      </c>
+      <c r="F21" s="4">
+        <v>60000015</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="2">
+        <v>4</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
+        <v>2</v>
+      </c>
+      <c r="N21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="5:13">
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:13">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="4"/>
-    </row>
-    <row r="25" customHeight="1" spans="12:13">
-      <c r="L25" s="2"/>
-      <c r="M25" s="4"/>
-    </row>
-    <row r="26" customHeight="1" spans="12:13">
-      <c r="L26" s="2"/>
-      <c r="M26" s="4"/>
-    </row>
-    <row r="27" customHeight="1" spans="12:13">
-      <c r="L27" s="2"/>
-      <c r="M27" s="4"/>
-    </row>
-    <row r="28" customHeight="1" spans="12:13">
-      <c r="L28" s="2"/>
-      <c r="M28" s="4"/>
-    </row>
-    <row r="29" customHeight="1" spans="12:13">
-      <c r="L29" s="2"/>
-      <c r="M29" s="4"/>
-    </row>
-    <row r="30" customHeight="1" spans="12:13">
-      <c r="L30" s="2"/>
-      <c r="M30" s="4"/>
-    </row>
-    <row r="31" customHeight="1" spans="12:13">
-      <c r="L31" s="2"/>
-      <c r="M31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="12:13">
-      <c r="L32" s="2"/>
-      <c r="M32" s="4"/>
-    </row>
-    <row r="33" customHeight="1" spans="12:13">
-      <c r="L33" s="2"/>
-      <c r="M33" s="4"/>
-    </row>
-    <row r="34" customHeight="1" spans="12:13">
-      <c r="L34" s="2"/>
-      <c r="M34" s="4"/>
-    </row>
-    <row r="35" customHeight="1" spans="12:13">
-      <c r="L35" s="2"/>
-      <c r="M35" s="4"/>
-    </row>
-    <row r="36" customHeight="1" spans="12:13">
-      <c r="L36" s="2"/>
-      <c r="M36" s="4"/>
-    </row>
-    <row r="37" customHeight="1" spans="12:13">
-      <c r="L37" s="2"/>
-      <c r="M37" s="4"/>
-    </row>
-    <row r="38" customHeight="1" spans="12:13">
-      <c r="L38" s="2"/>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" customHeight="1" spans="12:13">
-      <c r="L39" s="2"/>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" customHeight="1" spans="12:13">
-      <c r="L40" s="2"/>
-      <c r="M40" s="4"/>
-    </row>
-    <row r="41" customHeight="1" spans="12:13">
-      <c r="L41" s="2"/>
-      <c r="M41" s="4"/>
-    </row>
-    <row r="42" customHeight="1" spans="12:13">
-      <c r="L42" s="2"/>
-      <c r="M42" s="4"/>
-    </row>
-    <row r="43" customHeight="1" spans="12:13">
-      <c r="L43" s="2"/>
-      <c r="M43" s="4"/>
-    </row>
-    <row r="44" customHeight="1" spans="12:13">
-      <c r="L44" s="2"/>
-      <c r="M44" s="4"/>
-    </row>
-    <row r="45" customHeight="1" spans="12:13">
-      <c r="L45" s="2"/>
-      <c r="M45" s="4"/>
-    </row>
-    <row r="46" customHeight="1" spans="12:13">
-      <c r="L46" s="2"/>
-      <c r="M46" s="4"/>
-    </row>
-    <row r="47" customHeight="1" spans="12:13">
-      <c r="L47" s="2"/>
-      <c r="M47" s="4"/>
-    </row>
-    <row r="48" customHeight="1" spans="12:13">
-      <c r="L48" s="2"/>
-      <c r="M48" s="4"/>
-    </row>
-    <row r="49" customHeight="1" spans="12:13">
-      <c r="L49" s="2"/>
-      <c r="M49" s="4"/>
-    </row>
-    <row r="50" customHeight="1" spans="12:13">
-      <c r="L50" s="2"/>
-      <c r="M50" s="4"/>
-    </row>
-    <row r="51" customHeight="1" spans="12:13">
-      <c r="L51" s="2"/>
-      <c r="M51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="12:13">
-      <c r="L52" s="2"/>
-      <c r="M52" s="4"/>
-    </row>
-    <row r="53" customHeight="1" spans="12:13">
-      <c r="L53" s="2"/>
-      <c r="M53" s="4"/>
-    </row>
-    <row r="54" customHeight="1" spans="12:13">
-      <c r="L54" s="2"/>
-      <c r="M54" s="4"/>
-    </row>
-    <row r="55" customHeight="1" spans="12:13">
-      <c r="L55" s="2"/>
-      <c r="M55" s="4"/>
+      <c r="C22" s="1">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>11</v>
+      </c>
+      <c r="F22" s="4">
+        <v>60000016</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="2">
+        <v>16</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="4"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:14">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="1">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>11</v>
+      </c>
+      <c r="F23" s="4">
+        <v>60000017</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="2">
+        <v>16</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="4"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>11</v>
+      </c>
+      <c r="F24" s="4">
+        <v>60000018</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="2">
+        <v>16</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="N24" s="4"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:14">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="1">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2">
+        <v>11</v>
+      </c>
+      <c r="F25" s="4">
+        <v>60000019</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="2">
+        <v>10</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="4"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:14">
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>14</v>
+      </c>
+      <c r="F26" s="4">
+        <v>60000020</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="2">
+        <v>10</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="4"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:14">
+      <c r="C27" s="1">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>14</v>
+      </c>
+      <c r="F27" s="4">
+        <v>60000021</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I27" s="2">
+        <v>16</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="4"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:14">
+      <c r="C28" s="1">
+        <v>22</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>14</v>
+      </c>
+      <c r="F28" s="4">
+        <v>60000022</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" s="2">
+        <v>16</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="4"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
+      <c r="C29" s="1">
+        <v>23</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2">
+        <v>14</v>
+      </c>
+      <c r="F29" s="4">
+        <v>60000023</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="2">
+        <v>16</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="M29" s="2"/>
+      <c r="N29" s="4"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:14">
+      <c r="M30" s="2"/>
+      <c r="N30" s="4"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:14">
+      <c r="M31" s="2"/>
+      <c r="N31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:14">
+      <c r="M32" s="2"/>
+      <c r="N32" s="4"/>
+    </row>
+    <row r="33" customHeight="1" spans="13:14">
+      <c r="M33" s="2"/>
+      <c r="N33" s="4"/>
+    </row>
+    <row r="34" customHeight="1" spans="13:14">
+      <c r="M34" s="2"/>
+      <c r="N34" s="4"/>
+    </row>
+    <row r="35" customHeight="1" spans="13:14">
+      <c r="M35" s="2"/>
+      <c r="N35" s="4"/>
+    </row>
+    <row r="36" customHeight="1" spans="13:14">
+      <c r="M36" s="2"/>
+      <c r="N36" s="4"/>
+    </row>
+    <row r="37" customHeight="1" spans="13:14">
+      <c r="M37" s="2"/>
+      <c r="N37" s="4"/>
+    </row>
+    <row r="38" customHeight="1" spans="13:14">
+      <c r="M38" s="2"/>
+      <c r="N38" s="4"/>
+    </row>
+    <row r="39" customHeight="1" spans="13:14">
+      <c r="M39" s="2"/>
+      <c r="N39" s="4"/>
+    </row>
+    <row r="40" customHeight="1" spans="13:14">
+      <c r="M40" s="2"/>
+      <c r="N40" s="4"/>
+    </row>
+    <row r="41" customHeight="1" spans="13:14">
+      <c r="M41" s="2"/>
+      <c r="N41" s="4"/>
+    </row>
+    <row r="42" customHeight="1" spans="13:14">
+      <c r="M42" s="2"/>
+      <c r="N42" s="4"/>
+    </row>
+    <row r="43" customHeight="1" spans="13:14">
+      <c r="M43" s="2"/>
+      <c r="N43" s="4"/>
+    </row>
+    <row r="44" customHeight="1" spans="13:14">
+      <c r="M44" s="2"/>
+      <c r="N44" s="4"/>
+    </row>
+    <row r="45" customHeight="1" spans="13:14">
+      <c r="M45" s="2"/>
+      <c r="N45" s="4"/>
+    </row>
+    <row r="46" customHeight="1" spans="13:14">
+      <c r="M46" s="2"/>
+      <c r="N46" s="4"/>
+    </row>
+    <row r="47" customHeight="1" spans="13:14">
+      <c r="M47" s="2"/>
+      <c r="N47" s="4"/>
+    </row>
+    <row r="48" customHeight="1" spans="13:14">
+      <c r="M48" s="2"/>
+      <c r="N48" s="4"/>
+    </row>
+    <row r="49" customHeight="1" spans="13:14">
+      <c r="M49" s="2"/>
+      <c r="N49" s="4"/>
+    </row>
+    <row r="50" customHeight="1" spans="13:14">
+      <c r="M50" s="2"/>
+      <c r="N50" s="4"/>
+    </row>
+    <row r="51" customHeight="1" spans="13:14">
+      <c r="M51" s="2"/>
+      <c r="N51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="13:14">
+      <c r="M52" s="2"/>
+      <c r="N52" s="4"/>
+    </row>
+    <row r="53" customHeight="1" spans="13:14">
+      <c r="M53" s="2"/>
+      <c r="N53" s="4"/>
+    </row>
+    <row r="54" customHeight="1" spans="13:14">
+      <c r="M54" s="2"/>
+      <c r="N54" s="4"/>
+    </row>
+    <row r="55" customHeight="1" spans="13:14">
+      <c r="M55" s="2"/>
+      <c r="N55" s="4"/>
+    </row>
+    <row r="56" customHeight="1" spans="13:14">
+      <c r="M56" s="2"/>
+      <c r="N56" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5 E3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
